--- a/artfynd/A 46814-2023 artfynd.xlsx
+++ b/artfynd/A 46814-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 46814-2023 artfynd.xlsx
+++ b/artfynd/A 46814-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,59 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>16896201</v>
+        <v>98822703</v>
       </c>
       <c r="B2" t="n">
-        <v>82948</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>DD</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>263588</v>
+        <v>222498</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Liten klubbdyna</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Trichoderma seppoi</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Jaklitsch</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Ammerån, 800 m NO stranden vid Kvarnflyn, Jmt</t>
+          <t>Kvarnflyn, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>524305.7539195501</v>
+        <v>524053</v>
       </c>
       <c r="R2" t="n">
-        <v>7035555.948484605</v>
+        <v>7035518</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -754,61 +740,157 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2014-10-21</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-10-25</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2014-10-21</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-10-25</t>
         </is>
       </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>olikåldrig barrskog med inslag av gammal gran i svagt SV-lut, diffust kalkpåverkat, frisk mark nära fuktigare dråg</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>fyra fruktkroppar under gammal gran bland tunn väggmossa, linnea, lingon</t>
-        </is>
-      </c>
-      <c r="AQ2" t="inlineStr">
-        <is>
-          <t>Magnus Andersson</t>
-        </is>
-      </c>
-      <c r="AR2" t="inlineStr"/>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
+          <t>Sebastian Acker</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>Sebastian Acker</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>16896201</v>
+      </c>
+      <c r="B3" t="n">
+        <v>85076</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>DD</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>263588</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Liten klubbdyna</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Trichoderma seppoi</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Jaklitsch</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Ammerån, 800 m NO stranden vid Kvarnflyn, Jmt</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>524306</v>
+      </c>
+      <c r="R3" t="n">
+        <v>7035556</v>
+      </c>
+      <c r="S3" t="n">
+        <v>25</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2014-10-21</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2014-10-21</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>olikåldrig barrskog med inslag av gammal gran i svagt SV-lut, diffust kalkpåverkat, frisk mark nära fuktigare dråg</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>fyra fruktkroppar under gammal gran bland tunn väggmossa, linnea, lingon</t>
+        </is>
+      </c>
+      <c r="AQ3" t="inlineStr">
+        <is>
           <t>Magnus Andersson</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
+      <c r="AR3" t="inlineStr"/>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
         <is>
           <t>Magnus Andersson</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr">
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
         <is>
           <t>SCA Skog Naturvärdesinventering</t>
         </is>

--- a/artfynd/A 46814-2023 artfynd.xlsx
+++ b/artfynd/A 46814-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98822703</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -895,8 +905,17 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16896201</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>